--- a/output/yearly_surface_area_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_51_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497640654888</v>
+        <v>10.84497631541305</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789072200924</v>
+        <v>37.78907188336329</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.714753386420683</v>
+        <v>4.637776154861932</v>
       </c>
       <c r="C2" t="n">
-        <v>10.63723637551419</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="D2" t="n">
-        <v>23.22716893477529</v>
+        <v>43.2440228766635</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.9280957378785</v>
+        <v>15.0060136594125</v>
       </c>
       <c r="C3" t="n">
-        <v>30.5470798176395</v>
+        <v>51.72828653676444</v>
       </c>
       <c r="D3" t="n">
-        <v>53.76050428455534</v>
+        <v>73.64089529555325</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.84521232456105</v>
+        <v>32.91505528028281</v>
       </c>
       <c r="C4" t="n">
-        <v>93.07851809193585</v>
+        <v>100.493658502112</v>
       </c>
       <c r="D4" t="n">
-        <v>77.08682973745954</v>
+        <v>83.83830869956486</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.23464736797755</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="C5" t="n">
-        <v>169.4987411382118</v>
+        <v>155.4842926600886</v>
       </c>
       <c r="D5" t="n">
-        <v>61.87464906015524</v>
+        <v>62.41461029749098</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.31707311740527</v>
+        <v>35.98498035146259</v>
       </c>
       <c r="C6" t="n">
-        <v>200.8960144677291</v>
+        <v>174.9336964289222</v>
       </c>
       <c r="D6" t="n">
-        <v>45.08185457901354</v>
+        <v>43.99505987041232</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.64387192973244</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>161.7537334994087</v>
+        <v>139.4759145946401</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>97.55136063248432</v>
+        <v>89.79064503041327</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>48.03593342109217</v>
       </c>
       <c r="D9" t="n">
         <v>34.05780960802609</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.630808451706242</v>
+        <v>7.655555377939586</v>
       </c>
       <c r="C21" t="n">
-        <v>91.56970142047491</v>
+        <v>92.82360895751748</v>
       </c>
       <c r="D21" t="n">
-        <v>7.630808451706242</v>
+        <v>7.655555377939586</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.411213419359171</v>
+        <v>6.137886646951058</v>
       </c>
       <c r="C2" t="n">
-        <v>14.51415805958485</v>
+        <v>7.948229413582177</v>
       </c>
       <c r="D2" t="n">
-        <v>23.19967999905638</v>
+        <v>42.57741618547992</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6826588118168</v>
+        <v>15.03055735201867</v>
       </c>
       <c r="C3" t="n">
-        <v>35.40673095366122</v>
+        <v>49.34754835396592</v>
       </c>
       <c r="D3" t="n">
-        <v>58.21763886183585</v>
+        <v>87.05647767408591</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.31819373382976</v>
+        <v>30.63052837250048</v>
       </c>
       <c r="C4" t="n">
-        <v>84.20842758406592</v>
+        <v>112.4523272875424</v>
       </c>
       <c r="D4" t="n">
-        <v>84.36158022592842</v>
+        <v>97.81348726951822</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.25981295538948</v>
+        <v>43.93320976504477</v>
       </c>
       <c r="C5" t="n">
-        <v>170.0632460681537</v>
+        <v>167.068915570201</v>
       </c>
       <c r="D5" t="n">
-        <v>71.8148445656542</v>
+        <v>74.14649536324036</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.45419900083034</v>
+        <v>43.71329827929349</v>
       </c>
       <c r="C6" t="n">
-        <v>228.9111669561161</v>
+        <v>207.1350211282176</v>
       </c>
       <c r="D6" t="n">
-        <v>52.56866257159972</v>
+        <v>51.80388110999145</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.64493579289469</v>
+        <v>32.21899615797182</v>
       </c>
       <c r="C7" t="n">
-        <v>218.1070334708799</v>
+        <v>187.7445222216388</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>41.50142070162541</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1138670381594</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C8" t="n">
-        <v>146.6191108907399</v>
+        <v>131.7652681254856</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>79.09843078346124</v>
+        <v>74.77186865084555</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.793854865205059</v>
+        <v>7.820676714363819</v>
       </c>
       <c r="C21" t="n">
-        <v>99.3716495313645</v>
+        <v>100.6912126974342</v>
       </c>
       <c r="D21" t="n">
-        <v>8.768086723355692</v>
+        <v>8.798261303659295</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.237444075707486</v>
+        <v>6.318528224532471</v>
       </c>
       <c r="C2" t="n">
-        <v>13.01012057667873</v>
+        <v>7.406304680837938</v>
       </c>
       <c r="D2" t="n">
-        <v>25.33988999431442</v>
+        <v>31.63878326476195</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.87686493080842</v>
+        <v>16.91551294417254</v>
       </c>
       <c r="C3" t="n">
-        <v>43.85466994870502</v>
+        <v>40.82597828110361</v>
       </c>
       <c r="D3" t="n">
-        <v>61.05488972710914</v>
+        <v>95.71549242554278</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.36549755008285</v>
+        <v>29.13729011434109</v>
       </c>
       <c r="C4" t="n">
-        <v>84.73169911042947</v>
+        <v>116.4981095767435</v>
       </c>
       <c r="D4" t="n">
-        <v>89.98993981437538</v>
+        <v>111.1632925518663</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.62796834448203</v>
+        <v>44.1541029985003</v>
       </c>
       <c r="C5" t="n">
-        <v>161.7674779672682</v>
+        <v>180.8624708148687</v>
       </c>
       <c r="D5" t="n">
-        <v>81.77958376375932</v>
+        <v>87.20373982972295</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.89446394068941</v>
+        <v>49.14727182229959</v>
       </c>
       <c r="C6" t="n">
-        <v>243.4822663825472</v>
+        <v>228.4281470856266</v>
       </c>
       <c r="D6" t="n">
-        <v>59.49194738194822</v>
+        <v>59.33094075845175</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.38838084691679</v>
+        <v>39.46527596301753</v>
       </c>
       <c r="C7" t="n">
-        <v>263.620857039762</v>
+        <v>230.6233349523225</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.79113408536946</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="C8" t="n">
-        <v>200.6103258857932</v>
+        <v>178.7468045122168</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.97656122828509</v>
+        <v>13.09062388842696</v>
       </c>
       <c r="C9" t="n">
-        <v>117.9265524864226</v>
+        <v>108.3859282965521</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>61.92373644536757</v>
+        <v>59.78843518863076</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>39.27088991757665</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.32797015314322</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.939746731343764</v>
+        <v>7.967627130995109</v>
       </c>
       <c r="C21" t="n">
-        <v>106.1941125317228</v>
+        <v>107.562966268434</v>
       </c>
       <c r="D21" t="n">
-        <v>9.924683414179704</v>
+        <v>9.959533913743886</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.829037030740813</v>
+        <v>5.896376711706344</v>
       </c>
       <c r="C2" t="n">
-        <v>9.262789589568657</v>
+        <v>5.272966919509619</v>
       </c>
       <c r="D2" t="n">
-        <v>20.9750397012331</v>
+        <v>26.41294023505619</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.21480712524758</v>
+        <v>19.777307502052</v>
       </c>
       <c r="C3" t="n">
-        <v>62.52751128347936</v>
+        <v>62.23789571072654</v>
       </c>
       <c r="D3" t="n">
-        <v>66.05689428024664</v>
+        <v>99.91737259971913</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.75516927321083</v>
+        <v>21.21164089795658</v>
       </c>
       <c r="C4" t="n">
-        <v>123.8621991062988</v>
+        <v>150.6766741523919</v>
       </c>
       <c r="D4" t="n">
-        <v>87.67988746628264</v>
+        <v>103.2759314959475</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.72303364087794</v>
+        <v>27.68528525976006</v>
       </c>
       <c r="C5" t="n">
-        <v>145.4950097693773</v>
+        <v>136.4874745829128</v>
       </c>
       <c r="D5" t="n">
-        <v>56.74501730546565</v>
+        <v>58.04583301359268</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.02773528209295</v>
+        <v>24.47300677146449</v>
       </c>
       <c r="C6" t="n">
-        <v>173.6053917850763</v>
+        <v>151.8694976130519</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>29.98748362621883</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>141.0329664535755</v>
+        <v>125.7019943040573</v>
       </c>
       <c r="D7" t="n">
-        <v>27.42806736124739</v>
+        <v>27.60772719112455</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>86.86994561027902</v>
+        <v>79.86026700195679</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>47.25937098703294</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
-        <v>26.95781021091316</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>28.04362317181014</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>23.43235420496287</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>23.96838845148163</v>
@@ -1898,10 +1898,10 @@
         <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.37631247036279</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.186172210908399</v>
+        <v>3.609886308515522</v>
       </c>
       <c r="C2" t="n">
-        <v>4.522911673465055</v>
+        <v>3.401755795215198</v>
       </c>
       <c r="D2" t="n">
-        <v>14.80671887545039</v>
+        <v>18.30174070256904</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.40624792757571</v>
+        <v>20.42035224833366</v>
       </c>
       <c r="C3" t="n">
-        <v>50.79562621772997</v>
+        <v>42.98091449192536</v>
       </c>
       <c r="D3" t="n">
-        <v>67.32334881872502</v>
+        <v>98.43493356630644</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.05093737409637</v>
+        <v>27.92483169959628</v>
       </c>
       <c r="C4" t="n">
-        <v>141.5640919615731</v>
+        <v>156.6879153454952</v>
       </c>
       <c r="D4" t="n">
-        <v>98.79621672146926</v>
+        <v>124.6534877559218</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.42913122440965</v>
+        <v>30.75324683553134</v>
       </c>
       <c r="C5" t="n">
-        <v>185.0348985579176</v>
+        <v>199.0493470360408</v>
       </c>
       <c r="D5" t="n">
-        <v>68.99231991594461</v>
+        <v>73.58199043329844</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.93843729873549</v>
+        <v>28.53842401475054</v>
       </c>
       <c r="C6" t="n">
-        <v>203.1903588525539</v>
+        <v>182.5010077332566</v>
       </c>
       <c r="D6" t="n">
-        <v>36.30699359845555</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.26541603751191</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>182.1151808854876</v>
+        <v>161.2746406197363</v>
       </c>
       <c r="D7" t="n">
-        <v>30.00319158948677</v>
+        <v>30.12296480940488</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>114.658314378985</v>
+        <v>104.8113849053895</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
         <v>24.97566159603886</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.756166716448297</v>
+        <v>3.524474258246049</v>
       </c>
       <c r="C2" t="n">
-        <v>15.8346087217968</v>
+        <v>5.904230693340318</v>
       </c>
       <c r="D2" t="n">
-        <v>18.45391159672729</v>
+        <v>18.31352167502</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.37969968183204</v>
+        <v>16.38536918387927</v>
       </c>
       <c r="C3" t="n">
-        <v>34.21881623152257</v>
+        <v>27.98471830955533</v>
       </c>
       <c r="D3" t="n">
-        <v>63.76451339083034</v>
+        <v>91.08655200001907</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.64100880207771</v>
+        <v>32.86400439966198</v>
       </c>
       <c r="C4" t="n">
-        <v>134.2382905924834</v>
+        <v>132.7195268940135</v>
       </c>
       <c r="D4" t="n">
-        <v>107.5003918673215</v>
+        <v>141.0280577150543</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.245986372072</v>
+        <v>35.4901795085222</v>
       </c>
       <c r="C5" t="n">
-        <v>219.6905925178301</v>
+        <v>241.9762654042326</v>
       </c>
       <c r="D5" t="n">
-        <v>84.30758410219485</v>
+        <v>95.25407100454679</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.29819892684633</v>
+        <v>33.81139093426016</v>
       </c>
       <c r="C6" t="n">
-        <v>245.6558557997497</v>
+        <v>240.2621339126177</v>
       </c>
       <c r="D6" t="n">
-        <v>46.12839763174064</v>
+        <v>46.97368240509714</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.88908787161589</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="C7" t="n">
-        <v>230.3239019025272</v>
+        <v>207.0878972384137</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>168.8998750386212</v>
+        <v>150.3742958594839</v>
       </c>
       <c r="D8" t="n">
         <v>28.70630287217673</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>86.97499261463339</v>
+        <v>80.09686819868024</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.48354395430394</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.315942834318226</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C2" t="n">
-        <v>7.880488821989147</v>
+        <v>2.922662915542754</v>
       </c>
       <c r="D2" t="n">
-        <v>13.02386504453819</v>
+        <v>12.91783629247953</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.59921025695582</v>
+        <v>16.08593613408399</v>
       </c>
       <c r="C3" t="n">
-        <v>46.73119072214817</v>
+        <v>27.74419012201486</v>
       </c>
       <c r="D3" t="n">
-        <v>65.17332134642452</v>
+        <v>89.23595757751383</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.26562132615693</v>
+        <v>35.91429451675682</v>
       </c>
       <c r="C4" t="n">
-        <v>132.1452044870292</v>
+        <v>126.1212005737707</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6985660348591</v>
+        <v>151.8125562462055</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.47317100238052</v>
+        <v>36.47192721276901</v>
       </c>
       <c r="C5" t="n">
-        <v>264.4828315240908</v>
+        <v>284.6577468463627</v>
       </c>
       <c r="D5" t="n">
-        <v>86.59014751456868</v>
+        <v>98.17477042468106</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.32207966691774</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="C6" t="n">
-        <v>280.5942930984851</v>
+        <v>270.9741473445707</v>
       </c>
       <c r="D6" t="n">
-        <v>45.36361617013237</v>
+        <v>46.12839763174064</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>229.9645822427728</v>
+        <v>206.0099382591507</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>110.402438081075</v>
+        <v>100.3051629428966</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>30.7296848906294</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>18.65811511921063</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
         <v>20.61179305066178</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.577087723647877</v>
+        <v>2.21285932537231</v>
       </c>
       <c r="C2" t="n">
-        <v>11.3715836582908</v>
+        <v>3.723769042208152</v>
       </c>
       <c r="D2" t="n">
-        <v>14.66829244915159</v>
+        <v>12.06077054667207</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.66101930459437</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="C3" t="n">
-        <v>39.03919745937441</v>
+        <v>19.87548227247668</v>
       </c>
       <c r="D3" t="n">
-        <v>61.51631114810514</v>
+        <v>81.08254289374406</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.52614432068083</v>
+        <v>33.32346232524949</v>
       </c>
       <c r="C4" t="n">
-        <v>125.955285211753</v>
+        <v>100.8637773866131</v>
       </c>
       <c r="D4" t="n">
-        <v>119.0889417682508</v>
+        <v>158.7427132904838</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.54804586981054</v>
+        <v>43.34416114249668</v>
       </c>
       <c r="C5" t="n">
-        <v>254.6898981742288</v>
+        <v>261.3412388705009</v>
       </c>
       <c r="D5" t="n">
-        <v>101.9544990860313</v>
+        <v>121.2212977818749</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.22398701195107</v>
+        <v>34.65667570761666</v>
       </c>
       <c r="C6" t="n">
-        <v>341.2132868449087</v>
+        <v>348.3780815905019</v>
       </c>
       <c r="D6" t="n">
-        <v>56.83533809425636</v>
+        <v>59.8542122848153</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>304.1640919820425</v>
+        <v>283.3235517162913</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>182.5019894809608</v>
+        <v>164.3936530761284</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>62.67968217763759</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.806415775814131</v>
+        <v>1.601230505626548</v>
       </c>
       <c r="C2" t="n">
-        <v>6.121196935978863</v>
+        <v>2.651700549170635</v>
       </c>
       <c r="D2" t="n">
-        <v>11.39710909860122</v>
+        <v>8.947648576505429</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.79078992800419</v>
+        <v>10.31816837163398</v>
       </c>
       <c r="C3" t="n">
-        <v>41.88135706316893</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="D3" t="n">
-        <v>60.18113427032947</v>
+        <v>74.4704721056418</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>29.9030533236536</v>
       </c>
       <c r="C4" t="n">
-        <v>116.8299403007789</v>
+        <v>83.25122357242527</v>
       </c>
       <c r="D4" t="n">
-        <v>121.3096550752571</v>
+        <v>163.4521570277557</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.98416283467437</v>
+        <v>46.95208395560371</v>
       </c>
       <c r="C5" t="n">
-        <v>255.0825972559276</v>
+        <v>241.4363041668969</v>
       </c>
       <c r="D5" t="n">
-        <v>112.0174130545611</v>
+        <v>136.364756119882</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.10072876957248</v>
+        <v>39.44662275663685</v>
       </c>
       <c r="C6" t="n">
-        <v>376.4334857347631</v>
+        <v>385.6108632740622</v>
       </c>
       <c r="D6" t="n">
-        <v>66.29447722467438</v>
+        <v>71.56744414418399</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.61233283000952</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>363.7512688913026</v>
+        <v>353.271112148468</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>234.9911304885165</v>
+        <v>211.3751894628595</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>68.11561921605218</v>
+        <v>67.11718180083317</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.09302935219197</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.44775906859456</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.038509144643878</v>
+        <v>2.297289627937536</v>
       </c>
       <c r="C2" t="n">
-        <v>12.83929647613979</v>
+        <v>4.198934931063608</v>
       </c>
       <c r="D2" t="n">
-        <v>11.95965053313464</v>
+        <v>10.19054117008189</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.213702204356315</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C3" t="n">
-        <v>34.15991136926777</v>
+        <v>14.39733008277947</v>
       </c>
       <c r="D3" t="n">
-        <v>56.06761138953534</v>
+        <v>66.48886327011523</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.49464627868692</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="C4" t="n">
-        <v>111.3419706340393</v>
+        <v>66.90217905360313</v>
       </c>
       <c r="D4" t="n">
-        <v>122.343435407829</v>
+        <v>162.5332411765807</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.65880343394118</v>
+        <v>46.41212271826797</v>
       </c>
       <c r="C5" t="n">
-        <v>238.6628669023997</v>
+        <v>205.9461246583747</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7247544277043</v>
+        <v>154.4289138780233</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.07684802950107</v>
+        <v>46.89317909334891</v>
       </c>
       <c r="C6" t="n">
-        <v>388.0259626265094</v>
+        <v>386.2548897680481</v>
       </c>
       <c r="D6" t="n">
-        <v>78.97374882502193</v>
+        <v>88.15112636432112</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.008861091534</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="C7" t="n">
-        <v>428.967787136714</v>
+        <v>428.7282406968778</v>
       </c>
       <c r="D7" t="n">
-        <v>46.05280305851362</v>
+        <v>46.8912155979404</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>320.108656446715</v>
+        <v>304.169982468268</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>140.55780056472</v>
+        <v>129.9078014690506</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.30999559483051</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.36962016288231</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.06233313145306</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.44775906859456</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.732825755724625</v>
+        <v>4.723188205131405</v>
       </c>
       <c r="C2" t="n">
-        <v>11.54535300194249</v>
+        <v>10.87383757223767</v>
       </c>
       <c r="D2" t="n">
-        <v>15.38104128243478</v>
+        <v>8.591274159863838</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.267837196810132</v>
+        <v>1.695478285234242</v>
       </c>
       <c r="C2" t="n">
-        <v>7.806857744170636</v>
+        <v>2.521128104505809</v>
       </c>
       <c r="D2" t="n">
-        <v>8.992808970900782</v>
+        <v>7.58105577219387</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.65963664626262</v>
+        <v>10.8973995171396</v>
       </c>
       <c r="C3" t="n">
-        <v>44.3848137089983</v>
+        <v>17.5438314748905</v>
       </c>
       <c r="D3" t="n">
-        <v>60.30876147188157</v>
+        <v>71.48105034621027</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.08319617961627</v>
+        <v>35.1357685872891</v>
       </c>
       <c r="C4" t="n">
-        <v>151.6849290446534</v>
+        <v>101.4380997935974</v>
       </c>
       <c r="D4" t="n">
-        <v>124.1046907892478</v>
+        <v>163.592546949463</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.15223731408305</v>
+        <v>26.4090132442392</v>
       </c>
       <c r="C5" t="n">
-        <v>341.4027641518284</v>
+        <v>320.0742952770664</v>
       </c>
       <c r="D5" t="n">
-        <v>111.9437819767426</v>
+        <v>136.5611056607314</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.7446888436336</v>
+        <v>14.20883452356409</v>
       </c>
       <c r="C6" t="n">
-        <v>343.3868762621112</v>
+        <v>346.7277636996631</v>
       </c>
       <c r="D6" t="n">
-        <v>64.60390767796137</v>
+        <v>69.47435803872979</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>225.1137668360894</v>
+        <v>213.914970773746</v>
       </c>
       <c r="D7" t="n">
-        <v>29.40432548989622</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.335176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>103.5596565824748</v>
+        <v>95.71549242554278</v>
       </c>
       <c r="D8" t="n">
-        <v>23.36559536107409</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>19.30312336090078</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>19.78712497909446</v>
+        <v>20.35653864755762</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.39340309196248</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.45958109877452</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.365873098514571</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.105709956889166</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.370961763485052</v>
+        <v>6.110397711232148</v>
       </c>
       <c r="C2" t="n">
-        <v>8.226064013884024</v>
+        <v>5.258240703945916</v>
       </c>
       <c r="D2" t="n">
-        <v>14.21668850519806</v>
+        <v>14.03997391843363</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.29915531235479</v>
+        <v>10.03837027592364</v>
       </c>
       <c r="C3" t="n">
-        <v>29.09409321535422</v>
+        <v>27.40057842552848</v>
       </c>
       <c r="D3" t="n">
-        <v>16.05648370295658</v>
+        <v>10.35252954128262</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3962276116298</v>
+        <v>13.39784946920401</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13319161382663</v>
+        <v>70.14168251524453</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5760267778388</v>
+        <v>1.576217584612237</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.663301595172349</v>
+        <v>3.917173339944773</v>
       </c>
       <c r="C2" t="n">
-        <v>10.16501572977148</v>
+        <v>9.40612475438869</v>
       </c>
       <c r="D2" t="n">
-        <v>13.90645623065607</v>
+        <v>19.41209735607218</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.00449213236051</v>
+        <v>16.65534980254714</v>
       </c>
       <c r="C3" t="n">
-        <v>30.9643225919444</v>
+        <v>23.08579726536375</v>
       </c>
       <c r="D3" t="n">
-        <v>24.1166323548229</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.5915362017711</v>
+        <v>11.76722798310227</v>
       </c>
       <c r="C4" t="n">
-        <v>44.8737240657132</v>
+        <v>42.29565459436108</v>
       </c>
       <c r="D4" t="n">
-        <v>23.4834050855837</v>
+        <v>20.49692856926491</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.63391558396972</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43539633433653</v>
+        <v>15.44014415819952</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11326375998273</v>
+        <v>86.13975161942892</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249557123018216</v>
+        <v>3.25055666488411</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.76187727622453</v>
+        <v>4.847870163570749</v>
       </c>
       <c r="C2" t="n">
-        <v>14.4356182432451</v>
+        <v>9.988301143007048</v>
       </c>
       <c r="D2" t="n">
-        <v>21.08990418262998</v>
+        <v>24.06950846501905</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.44213062427633</v>
+        <v>14.91274762750905</v>
       </c>
       <c r="C3" t="n">
-        <v>36.06450191550658</v>
+        <v>31.28339059582461</v>
       </c>
       <c r="D3" t="n">
-        <v>29.64387192973244</v>
+        <v>30.61580215693678</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.81371428256714</v>
+        <v>23.38130332434203</v>
       </c>
       <c r="C4" t="n">
-        <v>63.77531261557705</v>
+        <v>51.44652494564561</v>
       </c>
       <c r="D4" t="n">
-        <v>30.29869764846506</v>
+        <v>25.74240655305561</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.33351648200343</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="C5" t="n">
-        <v>48.76831720846032</v>
+        <v>46.82936549257286</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09685853201772</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7220665990729</v>
+        <v>16.73138346786113</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0046062543447</v>
+        <v>102.0614391539529</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180516649768224</v>
+        <v>4.182845866965282</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.290458451736814</v>
+        <v>5.814891652253858</v>
       </c>
       <c r="C2" t="n">
-        <v>12.41223622479242</v>
+        <v>14.24319569321272</v>
       </c>
       <c r="D2" t="n">
-        <v>23.13979338909732</v>
+        <v>24.99529655012379</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.08517537055799</v>
+        <v>15.77668560724624</v>
       </c>
       <c r="C3" t="n">
-        <v>47.33496556025997</v>
+        <v>35.58344554042564</v>
       </c>
       <c r="D3" t="n">
-        <v>39.07846736754428</v>
+        <v>42.09734155810323</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.00439432136928</v>
+        <v>26.15081359802229</v>
       </c>
       <c r="C4" t="n">
-        <v>78.27376271189394</v>
+        <v>66.44272112801563</v>
       </c>
       <c r="D4" t="n">
-        <v>37.90527886096935</v>
+        <v>34.77841242294325</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.03518835309942</v>
+        <v>22.80109043113217</v>
       </c>
       <c r="C5" t="n">
-        <v>85.338419191654</v>
+        <v>72.84567965511334</v>
       </c>
       <c r="D5" t="n">
-        <v>34.82749980815561</v>
+        <v>32.20132469929538</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.5585166327252</v>
+        <v>10.06291396852981</v>
       </c>
       <c r="C6" t="n">
-        <v>45.2026095466359</v>
+        <v>44.19631814978292</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.43940636534185</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03417767428143</v>
+        <v>18.05182220180488</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6515400655503</v>
+        <v>117.7666496022509</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011392558093811</v>
+        <v>6.017274067268294</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.378815745119026</v>
+        <v>5.832563110930301</v>
       </c>
       <c r="C2" t="n">
-        <v>9.50724476792611</v>
+        <v>8.897579443588842</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8075617544344</v>
+        <v>20.36930136771282</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.92456965768902</v>
+        <v>16.00248757922301</v>
       </c>
       <c r="C3" t="n">
-        <v>44.76769531365456</v>
+        <v>43.80558256349268</v>
       </c>
       <c r="D3" t="n">
-        <v>44.56152829576273</v>
+        <v>48.6652336995144</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.15532142591602</v>
+        <v>20.56074217004095</v>
       </c>
       <c r="C4" t="n">
-        <v>83.41713893444297</v>
+        <v>65.90668688149688</v>
       </c>
       <c r="D4" t="n">
-        <v>41.2746369819444</v>
+        <v>41.31292514241003</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.73375075016664</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="C5" t="n">
-        <v>85.338419191654</v>
+        <v>73.0420291959627</v>
       </c>
       <c r="D5" t="n">
-        <v>32.66765485881262</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.96732458831938</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>61.3032718962836</v>
+        <v>54.82275530055039</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>30.99377502307181</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>27.24840753137022</v>
+        <v>27.008861091534</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
         <v>30.28593492830985</v>
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.12167996206437</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.040874909687288</v>
+        <v>7.051746655593262</v>
       </c>
       <c r="C21" t="n">
-        <v>66.00820227831832</v>
+        <v>66.11012489618683</v>
       </c>
       <c r="D21" t="n">
-        <v>4.400546818554555</v>
+        <v>4.407341659745788</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.717698629533423</v>
+        <v>4.98040610364407</v>
       </c>
       <c r="C2" t="n">
-        <v>7.863799111016951</v>
+        <v>11.7721367216235</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64986022694915</v>
+        <v>26.69077483535803</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.37050409959532</v>
+        <v>18.67284133477433</v>
       </c>
       <c r="C3" t="n">
-        <v>39.95713156284518</v>
+        <v>38.0427235395639</v>
       </c>
       <c r="D3" t="n">
-        <v>52.1111681414207</v>
+        <v>54.01575868765951</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.43832680664636</v>
+        <v>27.18459393059418</v>
       </c>
       <c r="C4" t="n">
-        <v>100.9914045881651</v>
+        <v>93.09128081209106</v>
       </c>
       <c r="D4" t="n">
-        <v>55.04561202941441</v>
+        <v>57.22803717595507</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.58773238414113</v>
+        <v>25.74633354387261</v>
       </c>
       <c r="C5" t="n">
-        <v>126.0809489178966</v>
+        <v>102.4453729381547</v>
       </c>
       <c r="D5" t="n">
-        <v>40.61981126321179</v>
+        <v>38.18998569520093</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.23149683621978</v>
+        <v>19.48180144307371</v>
       </c>
       <c r="C6" t="n">
-        <v>103.0039873818711</v>
+        <v>89.76119259928589</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.79766216193392</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>62.28207435741764</v>
+        <v>57.43125895073415</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>28.78975142703771</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.253504922894448</v>
+        <v>7.269425673027463</v>
       </c>
       <c r="C21" t="n">
-        <v>75.25511357502991</v>
+        <v>75.42029135765993</v>
       </c>
       <c r="D21" t="n">
-        <v>5.440128692170836</v>
+        <v>5.452069254770597</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.944081438586937</v>
+        <v>3.6471927212769</v>
       </c>
       <c r="C2" t="n">
-        <v>7.022441328477434</v>
+        <v>15.44583663091507</v>
       </c>
       <c r="D2" t="n">
-        <v>15.86700639603695</v>
+        <v>34.1795463233527</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.50027472300515</v>
+        <v>17.9905266803228</v>
       </c>
       <c r="C3" t="n">
-        <v>34.48879685019045</v>
+        <v>42.54403676353553</v>
       </c>
       <c r="D3" t="n">
-        <v>53.93231013279853</v>
+        <v>62.28698309593889</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.47509344006</v>
+        <v>31.94508854848696</v>
       </c>
       <c r="C4" t="n">
-        <v>100.4426076214912</v>
+        <v>94.32926466714628</v>
       </c>
       <c r="D4" t="n">
-        <v>68.0380611474167</v>
+        <v>70.10562181256049</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.98796665230434</v>
+        <v>33.55122779263475</v>
       </c>
       <c r="C5" t="n">
-        <v>157.5459628390069</v>
+        <v>139.7517856995335</v>
       </c>
       <c r="D5" t="n">
-        <v>50.2654824574367</v>
+        <v>50.11822030179968</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.01264921363075</v>
+        <v>27.81389420901639</v>
       </c>
       <c r="C6" t="n">
-        <v>154.6468618683661</v>
+        <v>129.288318667671</v>
       </c>
       <c r="D6" t="n">
-        <v>39.40637110076273</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>107.6761247063817</v>
+        <v>96.17789559424303</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>56.32777453116075</v>
+        <v>53.57397222074844</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.450430925720803</v>
+        <v>7.471352377840264</v>
       </c>
       <c r="C21" t="n">
-        <v>83.81734791435903</v>
+        <v>84.05271425070296</v>
       </c>
       <c r="D21" t="n">
-        <v>6.519127060005703</v>
+        <v>6.537433330610231</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_51_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631541305</v>
+        <v>10.84497634507395</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907188336329</v>
+        <v>37.78907198671602</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.637776154861932</v>
+        <v>7.911904748525045</v>
       </c>
       <c r="C2" t="n">
-        <v>12.24730261047896</v>
+        <v>12.63116596283946</v>
       </c>
       <c r="D2" t="n">
-        <v>43.2440228766635</v>
+        <v>24.95995363277091</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.0060136594125</v>
+        <v>20.26327261565417</v>
       </c>
       <c r="C3" t="n">
-        <v>51.72828653676444</v>
+        <v>30.24273802932299</v>
       </c>
       <c r="D3" t="n">
-        <v>73.64089529555325</v>
+        <v>79.90444564864789</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.91505528028281</v>
+        <v>38.54341486872977</v>
       </c>
       <c r="C4" t="n">
-        <v>100.493658502112</v>
+        <v>78.32481359251477</v>
       </c>
       <c r="D4" t="n">
-        <v>83.83830869956486</v>
+        <v>105.9178145680756</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.57072387799944</v>
+        <v>51.63992924338224</v>
       </c>
       <c r="C5" t="n">
-        <v>155.4842926600886</v>
+        <v>110.7902284242526</v>
       </c>
       <c r="D5" t="n">
-        <v>62.41461029749098</v>
+        <v>74.88280614142548</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.98498035146259</v>
+        <v>51.40136455125026</v>
       </c>
       <c r="C6" t="n">
-        <v>174.9336964289222</v>
+        <v>106.5461330987936</v>
       </c>
       <c r="D6" t="n">
-        <v>43.99505987041232</v>
+        <v>47.41645061971246</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>38.80652325346792</v>
       </c>
       <c r="C7" t="n">
-        <v>139.4759145946401</v>
+        <v>89.94968815850125</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>89.79064503041327</v>
+        <v>55.15949476310704</v>
       </c>
       <c r="D8" t="n">
         <v>35.63253292563798</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>8.985936736971052</v>
       </c>
       <c r="C9" t="n">
-        <v>48.03593342109217</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.655555377939586</v>
+        <v>7.682075542118325</v>
       </c>
       <c r="C21" t="n">
-        <v>92.82360895751748</v>
+        <v>93.14516594818468</v>
       </c>
       <c r="D21" t="n">
-        <v>7.655555377939586</v>
+        <v>8.642334984883115</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.137886646951058</v>
+        <v>9.455212139601031</v>
       </c>
       <c r="C2" t="n">
-        <v>7.948229413582177</v>
+        <v>11.08098633783375</v>
       </c>
       <c r="D2" t="n">
-        <v>42.57741618547992</v>
+        <v>25.34872572365264</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.03055735201867</v>
+        <v>23.15942834318226</v>
       </c>
       <c r="C3" t="n">
-        <v>49.34754835396592</v>
+        <v>39.55952374262523</v>
       </c>
       <c r="D3" t="n">
-        <v>87.05647767408591</v>
+        <v>80.63584768831177</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.63052837250048</v>
+        <v>38.09671966329748</v>
       </c>
       <c r="C4" t="n">
-        <v>112.4523272875424</v>
+        <v>76.07857484519808</v>
       </c>
       <c r="D4" t="n">
-        <v>97.81348726951822</v>
+        <v>119.3059080108894</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.93320976504477</v>
+        <v>54.36427912266713</v>
       </c>
       <c r="C5" t="n">
-        <v>167.068915570201</v>
+        <v>126.8172596960817</v>
       </c>
       <c r="D5" t="n">
-        <v>74.14649536324036</v>
+        <v>91.67069188404594</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.71329827929349</v>
+        <v>60.41773546705297</v>
       </c>
       <c r="C6" t="n">
-        <v>207.1350211282176</v>
+        <v>137.6606630894878</v>
       </c>
       <c r="D6" t="n">
-        <v>51.80388110999145</v>
+        <v>58.32464936159877</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.21899615797182</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="C7" t="n">
-        <v>187.7445222216388</v>
+        <v>120.1325395778652</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="C8" t="n">
-        <v>131.7652681254856</v>
+        <v>84.11614329986671</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="C9" t="n">
-        <v>74.77186865084555</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42131830050468</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.50740899884213</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.820676714363819</v>
+        <v>7.860145186244671</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6912126974342</v>
+        <v>101.1993692729001</v>
       </c>
       <c r="D21" t="n">
-        <v>8.798261303659295</v>
+        <v>9.825181482805839</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.318528224532471</v>
+        <v>12.1579635693925</v>
       </c>
       <c r="C2" t="n">
-        <v>7.406304680837938</v>
+        <v>11.3421312271634</v>
       </c>
       <c r="D2" t="n">
-        <v>31.63878326476195</v>
+        <v>20.47827536288422</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.91551294417254</v>
+        <v>26.4237394598029</v>
       </c>
       <c r="C3" t="n">
-        <v>40.82597828110361</v>
+        <v>40.83088701962485</v>
       </c>
       <c r="D3" t="n">
-        <v>95.71549242554278</v>
+        <v>81.00400307740432</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.13729011434109</v>
+        <v>39.74311056331938</v>
       </c>
       <c r="C4" t="n">
-        <v>116.4981095767435</v>
+        <v>85.33154695772427</v>
       </c>
       <c r="D4" t="n">
-        <v>111.1632925518663</v>
+        <v>127.5378625109989</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.1541029985003</v>
+        <v>55.10058990085224</v>
       </c>
       <c r="C5" t="n">
-        <v>180.8624708148687</v>
+        <v>132.3886779176824</v>
       </c>
       <c r="D5" t="n">
-        <v>87.20373982972295</v>
+        <v>108.7040145527281</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.14727182229959</v>
+        <v>65.65045073068846</v>
       </c>
       <c r="C6" t="n">
-        <v>228.4281470856266</v>
+        <v>163.4217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>59.33094075845175</v>
+        <v>69.35360307110744</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.46527596301753</v>
+        <v>58.56910453995621</v>
       </c>
       <c r="C7" t="n">
-        <v>230.6233349523225</v>
+        <v>154.0882474246496</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>48.56804067679396</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.70077223884975</v>
+        <v>39.8884092235479</v>
       </c>
       <c r="C8" t="n">
-        <v>178.7468045122168</v>
+        <v>115.0755571532899</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>20.41249826669968</v>
       </c>
       <c r="C9" t="n">
-        <v>108.3859282965521</v>
+        <v>71.88749389576842</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>59.78843518863076</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27088991757665</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.967627130995109</v>
+        <v>8.021722171522839</v>
       </c>
       <c r="C21" t="n">
-        <v>107.562966268434</v>
+        <v>109.2959645869987</v>
       </c>
       <c r="D21" t="n">
-        <v>9.959533913743886</v>
+        <v>11.0298679858439</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.896376711706344</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C2" t="n">
-        <v>5.272966919509619</v>
+        <v>7.802930753353649</v>
       </c>
       <c r="D2" t="n">
-        <v>26.41294023505619</v>
+        <v>17.15996812253</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.777307502052</v>
+        <v>29.68314183790231</v>
       </c>
       <c r="C3" t="n">
-        <v>62.23789571072654</v>
+        <v>59.09630305713676</v>
       </c>
       <c r="D3" t="n">
-        <v>99.91737259971913</v>
+        <v>88.94143326623978</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.21164089795658</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="C4" t="n">
-        <v>150.6766741523919</v>
+        <v>112.7713952914226</v>
       </c>
       <c r="D4" t="n">
-        <v>103.2759314959475</v>
+        <v>122.3179099675186</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.68528525976006</v>
+        <v>36.98734475749859</v>
       </c>
       <c r="C5" t="n">
-        <v>136.4874745829128</v>
+        <v>97.63480918734531</v>
       </c>
       <c r="D5" t="n">
-        <v>58.04583301359268</v>
+        <v>70.66129101316419</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.47300677146449</v>
+        <v>36.34724525432967</v>
       </c>
       <c r="C6" t="n">
-        <v>151.8694976130519</v>
+        <v>101.4744244586546</v>
       </c>
       <c r="D6" t="n">
-        <v>29.98748362621883</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>26.40999499194344</v>
       </c>
       <c r="C7" t="n">
-        <v>125.7019943040573</v>
+        <v>80.90681005468389</v>
       </c>
       <c r="D7" t="n">
-        <v>27.60772719112455</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>79.86026700195679</v>
+        <v>52.98983233672158</v>
       </c>
       <c r="D8" t="n">
-        <v>26.53664044579129</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.609886308515522</v>
+        <v>6.400013283984956</v>
       </c>
       <c r="C2" t="n">
-        <v>3.401755795215198</v>
+        <v>3.871031197845173</v>
       </c>
       <c r="D2" t="n">
-        <v>18.30174070256904</v>
+        <v>11.81042488208913</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.42035224833366</v>
+        <v>34.14027641518283</v>
       </c>
       <c r="C3" t="n">
-        <v>42.98091449192536</v>
+        <v>45.41564879845745</v>
       </c>
       <c r="D3" t="n">
-        <v>98.43493356630644</v>
+        <v>84.24377050141879</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.92483169959628</v>
+        <v>39.25812719742145</v>
       </c>
       <c r="C4" t="n">
-        <v>156.6879153454952</v>
+        <v>133.5873918645677</v>
       </c>
       <c r="D4" t="n">
-        <v>124.6534877559218</v>
+        <v>135.4507490072282</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.75324683553134</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="C5" t="n">
-        <v>199.0493470360408</v>
+        <v>147.4094177926586</v>
       </c>
       <c r="D5" t="n">
-        <v>73.58199043329844</v>
+        <v>90.39441986852508</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.53842401475054</v>
+        <v>42.82776185006286</v>
       </c>
       <c r="C6" t="n">
-        <v>182.5010077332566</v>
+        <v>127.9197623679509</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>40.53341746523807</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>24.61339669317178</v>
       </c>
       <c r="C7" t="n">
-        <v>161.2746406197363</v>
+        <v>105.6998665777328</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12296480940488</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>104.8113849053895</v>
+        <v>71.09816874155401</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.104687151455913</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47968338341173</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.524474258246049</v>
+        <v>5.859070298944964</v>
       </c>
       <c r="C2" t="n">
-        <v>5.904230693340318</v>
+        <v>5.747151060660827</v>
       </c>
       <c r="D2" t="n">
-        <v>18.31352167502</v>
+        <v>16.543430564263</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38536918387927</v>
+        <v>27.91108723173682</v>
       </c>
       <c r="C3" t="n">
-        <v>27.98471830955533</v>
+        <v>29.25608158655495</v>
       </c>
       <c r="D3" t="n">
-        <v>91.08655200001907</v>
+        <v>75.15278676009333</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.86400439966198</v>
+        <v>51.7400675092154</v>
       </c>
       <c r="C4" t="n">
-        <v>132.7195268940135</v>
+        <v>124.487572393904</v>
       </c>
       <c r="D4" t="n">
-        <v>141.0280577150543</v>
+        <v>144.9717382430137</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.4901795085222</v>
+        <v>48.79286090106649</v>
       </c>
       <c r="C5" t="n">
-        <v>241.9762654042326</v>
+        <v>194.7787445225672</v>
       </c>
       <c r="D5" t="n">
-        <v>95.25407100454679</v>
+        <v>113.7600152295992</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.81139093426016</v>
+        <v>48.42274201656544</v>
       </c>
       <c r="C6" t="n">
-        <v>240.2621339126177</v>
+        <v>178.1940805547258</v>
       </c>
       <c r="D6" t="n">
-        <v>46.97368240509714</v>
+        <v>55.50703345041042</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.15804568485051</v>
+        <v>35.2133266559246</v>
       </c>
       <c r="C7" t="n">
-        <v>207.0878972384137</v>
+        <v>141.2725128934118</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="C8" t="n">
-        <v>150.3742958594839</v>
+        <v>102.3079282595601</v>
       </c>
       <c r="D8" t="n">
-        <v>28.70630287217673</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>80.09686819868024</v>
+        <v>60.01718240372024</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>37.15424186722054</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.43235420496287</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.151009220004762</v>
+        <v>3.532328239880024</v>
       </c>
       <c r="C2" t="n">
-        <v>2.922662915542754</v>
+        <v>2.75183881500381</v>
       </c>
       <c r="D2" t="n">
-        <v>12.91783629247953</v>
+        <v>11.54535300194249</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.08593613408399</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="C3" t="n">
-        <v>27.74419012201486</v>
+        <v>28.2399727126595</v>
       </c>
       <c r="D3" t="n">
-        <v>89.23595757751383</v>
+        <v>74.2544876107075</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.91429451675682</v>
+        <v>57.03659637362694</v>
       </c>
       <c r="C4" t="n">
-        <v>126.1212005737707</v>
+        <v>118.5018566411112</v>
       </c>
       <c r="D4" t="n">
-        <v>151.8125562462055</v>
+        <v>152.4379295338107</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.47192721276901</v>
+        <v>51.14905539125883</v>
       </c>
       <c r="C5" t="n">
-        <v>284.6577468463627</v>
+        <v>232.2815068247954</v>
       </c>
       <c r="D5" t="n">
-        <v>98.17477042468106</v>
+        <v>119.7732199181109</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.56609287691869</v>
+        <v>41.09694064747573</v>
       </c>
       <c r="C6" t="n">
-        <v>270.9741473445707</v>
+        <v>210.1538953187765</v>
       </c>
       <c r="D6" t="n">
-        <v>46.12839763174064</v>
+        <v>54.13847715069036</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.006733365209485</v>
+        <v>11.19879606234337</v>
       </c>
       <c r="C7" t="n">
-        <v>206.0099382591507</v>
+        <v>143.0691111921834</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.588287859022091</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>100.3051629428966</v>
+        <v>74.2692138262712</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>18.65811511921063</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.21285932537231</v>
+        <v>4.223478623669778</v>
       </c>
       <c r="C2" t="n">
-        <v>3.723769042208152</v>
+        <v>3.309471511015998</v>
       </c>
       <c r="D2" t="n">
-        <v>12.06077054667207</v>
+        <v>12.07353326682727</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.03622685406589</v>
+        <v>20.04237938219863</v>
       </c>
       <c r="C3" t="n">
-        <v>19.87548227247668</v>
+        <v>19.48769192929919</v>
       </c>
       <c r="D3" t="n">
-        <v>81.08254289374406</v>
+        <v>67.72586537746621</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.32346232524949</v>
+        <v>54.52234050305086</v>
       </c>
       <c r="C4" t="n">
-        <v>100.8637773866131</v>
+        <v>95.2609432384765</v>
       </c>
       <c r="D4" t="n">
-        <v>158.7427132904838</v>
+        <v>154.0332695532118</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.34416114249668</v>
+        <v>65.31076602501908</v>
       </c>
       <c r="C5" t="n">
-        <v>261.3412388705009</v>
+        <v>227.7163800000477</v>
       </c>
       <c r="D5" t="n">
-        <v>121.2212977818749</v>
+        <v>141.0771451002667</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.65667570761666</v>
+        <v>52.1258943569844</v>
       </c>
       <c r="C6" t="n">
-        <v>348.3780815905019</v>
+        <v>280.7955513778558</v>
       </c>
       <c r="D6" t="n">
-        <v>59.8542122848153</v>
+        <v>72.53348388516285</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.95358012045992</v>
+        <v>22.81679839440012</v>
       </c>
       <c r="C7" t="n">
-        <v>283.3235517162913</v>
+        <v>212.2980323048515</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>164.3936530761284</v>
+        <v>119.7486762255047</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>62.67968217763759</v>
+        <v>51.14218315732908</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.601230505626548</v>
+        <v>2.986476516318797</v>
       </c>
       <c r="C2" t="n">
-        <v>2.651700549170635</v>
+        <v>2.229549036344507</v>
       </c>
       <c r="D2" t="n">
-        <v>8.947648576505429</v>
+        <v>8.970228773703107</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.31816837163398</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7450897542611</v>
+        <v>16.86151682043897</v>
       </c>
       <c r="D3" t="n">
-        <v>74.4704721056418</v>
+        <v>63.80869203752144</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.9030533236536</v>
+        <v>49.09818443708723</v>
       </c>
       <c r="C4" t="n">
-        <v>83.25122357242527</v>
+        <v>78.46520351422208</v>
       </c>
       <c r="D4" t="n">
-        <v>163.4521570277557</v>
+        <v>153.5738116276243</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.95208395560371</v>
+        <v>72.74750488468867</v>
       </c>
       <c r="C5" t="n">
-        <v>241.4363041668969</v>
+        <v>214.1437179888356</v>
       </c>
       <c r="D5" t="n">
-        <v>136.364756119882</v>
+        <v>155.8769917417874</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.44662275663685</v>
+        <v>61.3032718962836</v>
       </c>
       <c r="C6" t="n">
-        <v>385.6108632740622</v>
+        <v>320.2421741344926</v>
       </c>
       <c r="D6" t="n">
-        <v>71.56744414418399</v>
+        <v>85.29325879725866</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.45641487148353</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>353.271112148468</v>
+        <v>275.0591995419416</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60312155223958</v>
+        <v>45.27427712904591</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>211.3751894628595</v>
+        <v>158.3853571261379</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>67.11718180083317</v>
+        <v>58.46405753560178</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.09302935219197</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.06233313145306</v>
+      </c>
+      <c r="D14" t="n">
         <v>10.75504610002381</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.297289627937536</v>
+        <v>5.038329218194631</v>
       </c>
       <c r="C2" t="n">
-        <v>4.198934931063608</v>
+        <v>6.90070461315083</v>
       </c>
       <c r="D2" t="n">
-        <v>10.19054117008189</v>
+        <v>18.10833640483242</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.065057390387548</v>
+        <v>14.19116306488765</v>
       </c>
       <c r="C3" t="n">
-        <v>14.39733008277947</v>
+        <v>13.05724446648258</v>
       </c>
       <c r="D3" t="n">
-        <v>66.48886327011523</v>
+        <v>58.06055922915637</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.1170332654504</v>
+        <v>41.8744848292392</v>
       </c>
       <c r="C4" t="n">
-        <v>66.90217905360313</v>
+        <v>62.53732876052182</v>
       </c>
       <c r="D4" t="n">
-        <v>162.5332411765807</v>
+        <v>149.0813341329909</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.41212271826797</v>
+        <v>73.58199043329844</v>
       </c>
       <c r="C5" t="n">
-        <v>205.9461246583747</v>
+        <v>184.7894616318559</v>
       </c>
       <c r="D5" t="n">
-        <v>154.4289138780233</v>
+        <v>169.8668965273044</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.89317909334891</v>
+        <v>74.38506005537235</v>
       </c>
       <c r="C6" t="n">
-        <v>386.2548897680481</v>
+        <v>329.1780417385471</v>
       </c>
       <c r="D6" t="n">
-        <v>88.15112636432112</v>
+        <v>105.4593383901924</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.93657161431823</v>
+        <v>37.06981156465531</v>
       </c>
       <c r="C7" t="n">
-        <v>428.7282406968778</v>
+        <v>347.941203862112</v>
       </c>
       <c r="D7" t="n">
-        <v>46.8912155979404</v>
+        <v>54.37704184282233</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>304.169982468268</v>
+        <v>236.99389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>129.9078014690506</v>
+        <v>106.6109284472738</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>45.69544689416779</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>25.62557857625024</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.723188205131405</v>
+        <v>9.088038498212724</v>
       </c>
       <c r="C2" t="n">
-        <v>10.87383757223767</v>
+        <v>3.390956570468483</v>
       </c>
       <c r="D2" t="n">
-        <v>8.591274159863838</v>
+        <v>8.288895866955821</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.695478285234242</v>
+        <v>3.645229225868407</v>
       </c>
       <c r="C2" t="n">
-        <v>2.521128104505809</v>
+        <v>4.02909257822891</v>
       </c>
       <c r="D2" t="n">
-        <v>7.58105577219387</v>
+        <v>13.47252374537898</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.8973995171396</v>
+        <v>19.45333075965055</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5438314748905</v>
+        <v>18.85937339858123</v>
       </c>
       <c r="D3" t="n">
-        <v>71.48105034621027</v>
+        <v>64.65790380169493</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.1357685872891</v>
+        <v>56.39846036586651</v>
       </c>
       <c r="C4" t="n">
-        <v>101.4380997935974</v>
+        <v>94.32926466714628</v>
       </c>
       <c r="D4" t="n">
-        <v>163.592546949463</v>
+        <v>154.288523956316</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.4090132442392</v>
+        <v>43.245986372072</v>
       </c>
       <c r="C5" t="n">
-        <v>320.0742952770664</v>
+        <v>276.4110661306895</v>
       </c>
       <c r="D5" t="n">
-        <v>136.5611056607314</v>
+        <v>154.4289138780233</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.20883452356409</v>
+        <v>22.98369550412208</v>
       </c>
       <c r="C6" t="n">
-        <v>346.7277636996631</v>
+        <v>290.4559487876444</v>
       </c>
       <c r="D6" t="n">
-        <v>69.47435803872979</v>
+        <v>81.79136473621028</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.251949307092936</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>213.914970773746</v>
+        <v>166.6644355160512</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76364514965055</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.335176877775662</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>95.71549242554278</v>
+        <v>78.52509012418112</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83437204208531</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35653864755762</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>15.45958109877452</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.110397711232148</v>
+        <v>7.937430188835462</v>
       </c>
       <c r="C2" t="n">
-        <v>5.258240703945916</v>
+        <v>5.709844647899449</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03997391843363</v>
+        <v>13.32918858055894</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.03837027592364</v>
+        <v>19.29134238844982</v>
       </c>
       <c r="C3" t="n">
-        <v>27.40057842552848</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="D3" t="n">
-        <v>10.35252954128262</v>
+        <v>10.09727513817845</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39784946920401</v>
+        <v>13.39843681825034</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14168251524453</v>
+        <v>70.14475746025178</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576217584612237</v>
+        <v>1.57628668450004</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.917173339944773</v>
+        <v>6.126105674500097</v>
       </c>
       <c r="C2" t="n">
-        <v>9.40612475438869</v>
+        <v>8.103345550853172</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41209735607218</v>
+        <v>28.69255840431728</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.65534980254714</v>
+        <v>24.24425955637498</v>
       </c>
       <c r="C3" t="n">
-        <v>23.08579726536375</v>
+        <v>17.12658870058561</v>
       </c>
       <c r="D3" t="n">
-        <v>19.64477156197868</v>
+        <v>18.84955592153876</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.76722798310227</v>
+        <v>22.21989579021806</v>
       </c>
       <c r="C4" t="n">
-        <v>42.29565459436108</v>
+        <v>13.55400880483146</v>
       </c>
       <c r="D4" t="n">
-        <v>20.49692856926491</v>
+        <v>20.35653864755761</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44014415819952</v>
+        <v>15.44235287899692</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13975161942892</v>
+        <v>86.15207395650914</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25055666488411</v>
+        <v>3.251021658736194</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.847870163570749</v>
+        <v>5.238605749860979</v>
       </c>
       <c r="C2" t="n">
-        <v>9.988301143007048</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="D2" t="n">
-        <v>24.06950846501905</v>
+        <v>28.99395494952105</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.91274762750905</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="C3" t="n">
-        <v>31.28339059582461</v>
+        <v>25.86414326838222</v>
       </c>
       <c r="D3" t="n">
-        <v>30.61580215693678</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.38130332434203</v>
+        <v>36.34822700203391</v>
       </c>
       <c r="C4" t="n">
-        <v>51.44652494564561</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D4" t="n">
-        <v>25.74240655305561</v>
+        <v>25.23189774684727</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.57833151325938</v>
+        <v>18.62866268808323</v>
       </c>
       <c r="C5" t="n">
-        <v>46.82936549257286</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="D5" t="n">
-        <v>30.0414797499524</v>
+        <v>29.77149913128453</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73138346786113</v>
+        <v>16.735117543052</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0614391539529</v>
+        <v>102.0842170126172</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182845866965282</v>
+        <v>5.020535262915601</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.814891652253858</v>
+        <v>5.992587986722531</v>
       </c>
       <c r="C2" t="n">
-        <v>14.24319569321272</v>
+        <v>6.245878894418207</v>
       </c>
       <c r="D2" t="n">
-        <v>24.99529655012379</v>
+        <v>35.27615850899639</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.77668560724624</v>
+        <v>20.0227444281137</v>
       </c>
       <c r="C3" t="n">
-        <v>35.58344554042564</v>
+        <v>20.15528036818702</v>
       </c>
       <c r="D3" t="n">
-        <v>42.09734155810323</v>
+        <v>51.13923791421635</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.15081359802229</v>
+        <v>40.49611105247669</v>
       </c>
       <c r="C4" t="n">
-        <v>66.44272112801563</v>
+        <v>49.74908316500287</v>
       </c>
       <c r="D4" t="n">
-        <v>34.77841242294325</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.80109043113217</v>
+        <v>36.42283982755667</v>
       </c>
       <c r="C5" t="n">
-        <v>72.84567965511334</v>
+        <v>38.18998569520093</v>
       </c>
       <c r="D5" t="n">
-        <v>32.20132469929538</v>
+        <v>31.80862561759666</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.06291396852981</v>
+        <v>15.57739082328414</v>
       </c>
       <c r="C6" t="n">
-        <v>44.19631814978292</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05182220180488</v>
+        <v>18.05998295511477</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7666496022509</v>
+        <v>117.8198888024154</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017274067268294</v>
+        <v>6.879993506710388</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.832563110930301</v>
+        <v>6.856525966459724</v>
       </c>
       <c r="C2" t="n">
-        <v>8.897579443588842</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D2" t="n">
-        <v>20.36930136771282</v>
+        <v>31.77917318646925</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.00248757922301</v>
+        <v>18.06906649666254</v>
       </c>
       <c r="C3" t="n">
-        <v>43.80558256349268</v>
+        <v>21.1468455494763</v>
       </c>
       <c r="D3" t="n">
-        <v>48.6652336995144</v>
+        <v>62.63059479242527</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.56074217004095</v>
+        <v>28.57573042751191</v>
       </c>
       <c r="C4" t="n">
-        <v>65.90668688149688</v>
+        <v>41.93829843001524</v>
       </c>
       <c r="D4" t="n">
-        <v>41.31292514241003</v>
+        <v>47.01786105178824</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.8986433067511</v>
+        <v>30.06602344255857</v>
       </c>
       <c r="C5" t="n">
-        <v>73.0420291959627</v>
+        <v>49.50462798664542</v>
       </c>
       <c r="D5" t="n">
-        <v>29.89421759431538</v>
+        <v>30.38509144643879</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.14970867713103</v>
+        <v>17.63022527286423</v>
       </c>
       <c r="C6" t="n">
-        <v>54.82275530055039</v>
+        <v>27.81389420901639</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99377502307181</v>
+        <v>30.87302005544945</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>27.008861091534</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051746655593262</v>
+        <v>7.057732677492689</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11012489618683</v>
+        <v>66.16624385149396</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407341659745788</v>
+        <v>5.293299508119516</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.98040610364407</v>
+        <v>5.486006171331176</v>
       </c>
       <c r="C2" t="n">
-        <v>11.7721367216235</v>
+        <v>7.281622722398593</v>
       </c>
       <c r="D2" t="n">
-        <v>26.69077483535803</v>
+        <v>25.75222403009808</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.67284133477433</v>
+        <v>21.77025534167302</v>
       </c>
       <c r="C3" t="n">
-        <v>38.0427235395639</v>
+        <v>37.93964003061799</v>
       </c>
       <c r="D3" t="n">
-        <v>54.01575868765951</v>
+        <v>74.19067400993146</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.18459393059418</v>
+        <v>33.13202152292136</v>
       </c>
       <c r="C4" t="n">
-        <v>93.09128081209106</v>
+        <v>48.94503179522473</v>
       </c>
       <c r="D4" t="n">
-        <v>57.22803717595507</v>
+        <v>68.484756352849</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.74633354387261</v>
+        <v>38.04272353956391</v>
       </c>
       <c r="C5" t="n">
-        <v>102.4453729381547</v>
+        <v>66.70975650357077</v>
       </c>
       <c r="D5" t="n">
-        <v>38.18998569520093</v>
+        <v>41.55247158224626</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.48180144307371</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>89.76119259928589</v>
+        <v>57.39886127649402</v>
       </c>
       <c r="D6" t="n">
-        <v>34.01264921363075</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.82140403328509</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>57.43125895073415</v>
+        <v>30.42239785920016</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>28.87319998189869</v>
+        <v>20.5283444958008</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269425673027463</v>
+        <v>7.279310331732048</v>
       </c>
       <c r="C21" t="n">
-        <v>75.42029135765993</v>
+        <v>75.52284469172001</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452069254770597</v>
+        <v>6.369396540265542</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.6471927212769</v>
+        <v>5.997496725243765</v>
       </c>
       <c r="C2" t="n">
-        <v>15.44583663091507</v>
+        <v>7.437720607373835</v>
       </c>
       <c r="D2" t="n">
-        <v>34.1795463233527</v>
+        <v>26.161612822769</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.9905266803228</v>
+        <v>20.20927649192059</v>
       </c>
       <c r="C3" t="n">
-        <v>42.54403676353553</v>
+        <v>32.11296740591317</v>
       </c>
       <c r="D3" t="n">
-        <v>62.28698309593889</v>
+        <v>77.57770358958295</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.94508854848696</v>
+        <v>38.5817030291954</v>
       </c>
       <c r="C4" t="n">
-        <v>94.32926466714628</v>
+        <v>76.06581212504287</v>
       </c>
       <c r="D4" t="n">
-        <v>70.10562181256049</v>
+        <v>90.28348237794518</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.55122779263475</v>
+        <v>44.47317100238052</v>
       </c>
       <c r="C5" t="n">
-        <v>139.7517856995335</v>
+        <v>80.30696220738911</v>
       </c>
       <c r="D5" t="n">
-        <v>50.11822030179968</v>
+        <v>56.32777453116076</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.81389420901639</v>
+        <v>42.42524529132167</v>
       </c>
       <c r="C6" t="n">
-        <v>129.288318667671</v>
+        <v>84.16621243278331</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>39.7686360036298</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="C7" t="n">
-        <v>96.17789559424303</v>
+        <v>58.62899114991527</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>53.57397222074844</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>25.18281036163492</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.471352377840264</v>
+        <v>7.488090265025561</v>
       </c>
       <c r="C21" t="n">
-        <v>84.05271425070296</v>
+        <v>84.24101548153756</v>
       </c>
       <c r="D21" t="n">
-        <v>6.537433330610231</v>
+        <v>7.488090265025561</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_51_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634507395</v>
+        <v>10.84497656314201</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907198671602</v>
+        <v>37.78907274656918</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.911904748525045</v>
+        <v>0.833503800905542</v>
       </c>
       <c r="C2" t="n">
-        <v>12.63116596283946</v>
+        <v>2.105848825609408</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95995363277091</v>
+        <v>20.00507296943725</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.26327261565417</v>
+        <v>7.088218424661971</v>
       </c>
       <c r="C3" t="n">
-        <v>30.24273802932299</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="D3" t="n">
-        <v>79.90444564864789</v>
+        <v>70.20968706921064</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.54341486872977</v>
+        <v>12.62233023350124</v>
       </c>
       <c r="C4" t="n">
-        <v>78.32481359251477</v>
+        <v>122.0754182845696</v>
       </c>
       <c r="D4" t="n">
-        <v>105.9178145680756</v>
+        <v>69.6716893272834</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.63992924338224</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C5" t="n">
-        <v>110.7902284242526</v>
+        <v>134.2294548631452</v>
       </c>
       <c r="D5" t="n">
-        <v>74.88280614142548</v>
+        <v>45.28311285838414</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.40136455125026</v>
+        <v>9.378635818669782</v>
       </c>
       <c r="C6" t="n">
-        <v>106.5461330987936</v>
+        <v>57.47936458824226</v>
       </c>
       <c r="D6" t="n">
-        <v>47.41645061971246</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.80652325346792</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>89.94968815850125</v>
+        <v>29.88341836956866</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>29.64387192973244</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.02765316663493</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>55.15949476310704</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.985936736971052</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>25.02769422436394</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.47216389248049</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.682075542118325</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.14516594818468</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.642334984883115</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.455212139601031</v>
+        <v>1.08973995171396</v>
       </c>
       <c r="C2" t="n">
-        <v>11.08098633783375</v>
+        <v>3.217187226816798</v>
       </c>
       <c r="D2" t="n">
-        <v>25.34872572365264</v>
+        <v>15.95634543712341</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.15942834318226</v>
+        <v>4.800746273766903</v>
       </c>
       <c r="C3" t="n">
-        <v>39.55952374262523</v>
+        <v>16.69952844923824</v>
       </c>
       <c r="D3" t="n">
-        <v>80.63584768831177</v>
+        <v>70.59747741238813</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.09671966329748</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="C4" t="n">
-        <v>76.07857484519808</v>
+        <v>93.44863697643689</v>
       </c>
       <c r="D4" t="n">
-        <v>119.3059080108894</v>
+        <v>88.13934539187015</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.36427912266713</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C5" t="n">
-        <v>126.8172596960817</v>
+        <v>185.7957530287089</v>
       </c>
       <c r="D5" t="n">
-        <v>91.67069188404594</v>
+        <v>59.22393025868885</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.41773546705297</v>
+        <v>13.28304643845935</v>
       </c>
       <c r="C6" t="n">
-        <v>137.6606630894878</v>
+        <v>138.5864511745925</v>
       </c>
       <c r="D6" t="n">
-        <v>58.32464936159877</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.0471335564664</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>120.1325395778652</v>
+        <v>56.8323928511436</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.95803119509142</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>84.11614329986671</v>
+        <v>34.21390749300134</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.860145186244671</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1993692729001</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.825181482805839</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.1579635693925</v>
+        <v>0.5674501730546564</v>
       </c>
       <c r="C2" t="n">
-        <v>11.3421312271634</v>
+        <v>1.325359400733194</v>
       </c>
       <c r="D2" t="n">
-        <v>20.47827536288422</v>
+        <v>10.76977231558751</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.4237394598029</v>
+        <v>4.835107443415541</v>
       </c>
       <c r="C3" t="n">
-        <v>40.83088701962485</v>
+        <v>15.76195939168254</v>
       </c>
       <c r="D3" t="n">
-        <v>81.00400307740432</v>
+        <v>69.85134915716056</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.74311056331938</v>
+        <v>14.60055185755856</v>
       </c>
       <c r="C4" t="n">
-        <v>85.33154695772427</v>
+        <v>80.77525586231482</v>
       </c>
       <c r="D4" t="n">
-        <v>127.5378625109989</v>
+        <v>100.6723365842849</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.10058990085224</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C5" t="n">
-        <v>132.3886779176824</v>
+        <v>206.9769597478339</v>
       </c>
       <c r="D5" t="n">
-        <v>108.7040145527281</v>
+        <v>68.55053344903355</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.65045073068846</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>163.4217228489241</v>
+        <v>181.0116964659142</v>
       </c>
       <c r="D6" t="n">
-        <v>69.35360307110744</v>
+        <v>36.95102009244145</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.56910453995621</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>154.0882474246496</v>
+        <v>55.81432048183967</v>
       </c>
       <c r="D7" t="n">
-        <v>48.56804067679396</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.8884092235479</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>115.0755571532899</v>
+        <v>37.88564390688441</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.41249826669968</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>71.88749389576842</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.00617789032851</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.021722171522839</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2959645869987</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0298679858439</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.90819874188631</v>
+        <v>0.6243915399009714</v>
       </c>
       <c r="C2" t="n">
-        <v>7.802930753353649</v>
+        <v>4.30300018771377</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15996812253</v>
+        <v>13.46074277292802</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.68314183790231</v>
+        <v>3.347759671481623</v>
       </c>
       <c r="C3" t="n">
-        <v>59.09630305713676</v>
+        <v>9.773298395776997</v>
       </c>
       <c r="D3" t="n">
-        <v>88.94143326623978</v>
+        <v>63.17055602976101</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.4698816019025</v>
+        <v>12.17563502806894</v>
       </c>
       <c r="C4" t="n">
-        <v>112.7713952914226</v>
+        <v>58.84890263566655</v>
       </c>
       <c r="D4" t="n">
-        <v>122.3179099675186</v>
+        <v>111.5972250371434</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.98734475749859</v>
+        <v>19.36497346626834</v>
       </c>
       <c r="C5" t="n">
-        <v>97.63480918734531</v>
+        <v>178.8744317137689</v>
       </c>
       <c r="D5" t="n">
-        <v>70.66129101316419</v>
+        <v>86.86012813323656</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>16.14091400552181</v>
       </c>
       <c r="C6" t="n">
-        <v>101.4744244586546</v>
+        <v>255.4370081771607</v>
       </c>
       <c r="D6" t="n">
-        <v>31.95981476405067</v>
+        <v>48.02022545782425</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.40999499194344</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>80.90681005468389</v>
+        <v>153.0701750553457</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>52.98983233672158</v>
+        <v>55.32639187282899</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>36.0546844384641</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.17187226816798</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.400013283984956</v>
+        <v>0.3583379120500858</v>
       </c>
       <c r="C2" t="n">
-        <v>3.871031197845173</v>
+        <v>2.591813939211579</v>
       </c>
       <c r="D2" t="n">
-        <v>11.81042488208913</v>
+        <v>10.27202622953438</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34.14027641518283</v>
+        <v>2.84706834231575</v>
       </c>
       <c r="C3" t="n">
-        <v>45.41564879845745</v>
+        <v>13.56284453416968</v>
       </c>
       <c r="D3" t="n">
-        <v>84.24377050141879</v>
+        <v>60.09277697694727</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.25812719742145</v>
+        <v>10.13359980323558</v>
       </c>
       <c r="C4" t="n">
-        <v>133.5873918645677</v>
+        <v>43.58468933003715</v>
       </c>
       <c r="D4" t="n">
-        <v>135.4507490072282</v>
+        <v>117.3532118271425</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.57072387799944</v>
+        <v>20.24854640009047</v>
       </c>
       <c r="C5" t="n">
-        <v>147.4094177926586</v>
+        <v>154.2571080297801</v>
       </c>
       <c r="D5" t="n">
-        <v>90.39441986852508</v>
+        <v>103.0344215607028</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.82776185006286</v>
+        <v>19.60255641069606</v>
       </c>
       <c r="C6" t="n">
-        <v>127.9197623679509</v>
+        <v>282.244610989324</v>
       </c>
       <c r="D6" t="n">
-        <v>40.53341746523807</v>
+        <v>58.80766923208819</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>105.6998665777328</v>
+        <v>230.2041286826091</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>71.09816874155401</v>
+        <v>92.62789589568656</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.859070298944964</v>
+        <v>1.044579557318606</v>
       </c>
       <c r="C2" t="n">
-        <v>5.747151060660827</v>
+        <v>5.580253950938871</v>
       </c>
       <c r="D2" t="n">
-        <v>16.543430564263</v>
+        <v>11.46779493330699</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.91108723173682</v>
+        <v>2.032217747790897</v>
       </c>
       <c r="C3" t="n">
-        <v>29.25608158655495</v>
+        <v>11.66316272645211</v>
       </c>
       <c r="D3" t="n">
-        <v>75.15278676009333</v>
+        <v>54.864970451833</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.7400675092154</v>
+        <v>7.849072895453249</v>
       </c>
       <c r="C4" t="n">
-        <v>124.487572393904</v>
+        <v>39.01563551447249</v>
       </c>
       <c r="D4" t="n">
-        <v>144.9717382430137</v>
+        <v>120.1227221008227</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.79286090106649</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="C5" t="n">
-        <v>194.7787445225672</v>
+        <v>118.5705789804085</v>
       </c>
       <c r="D5" t="n">
-        <v>113.7600152295992</v>
+        <v>118.7178411360456</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.42274201656544</v>
+        <v>23.14470212761856</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1940805547258</v>
+        <v>266.5867168542917</v>
       </c>
       <c r="D6" t="n">
-        <v>55.50703345041042</v>
+        <v>73.86178852900879</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.2133266559246</v>
+        <v>14.43267300013236</v>
       </c>
       <c r="C7" t="n">
-        <v>141.2725128934118</v>
+        <v>314.1651558452048</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.94005663677871</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3079282595601</v>
+        <v>185.0888946816511</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>60.01718240372024</v>
+        <v>75.54843108490478</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.532328239880024</v>
+        <v>0.7019496085364695</v>
       </c>
       <c r="C2" t="n">
-        <v>2.75183881500381</v>
+        <v>2.902046213753571</v>
       </c>
       <c r="D2" t="n">
-        <v>11.54535300194249</v>
+        <v>8.256498192715675</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.24840753137022</v>
+        <v>3.220132469929538</v>
       </c>
       <c r="C3" t="n">
-        <v>28.2399727126595</v>
+        <v>17.10204500797944</v>
       </c>
       <c r="D3" t="n">
-        <v>74.2544876107075</v>
+        <v>58.9441321629785</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.03659637362694</v>
+        <v>12.68614383427728</v>
       </c>
       <c r="C4" t="n">
-        <v>118.5018566411112</v>
+        <v>57.78959686278425</v>
       </c>
       <c r="D4" t="n">
-        <v>152.4379295338107</v>
+        <v>124.5513859946801</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.14905539125883</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="C5" t="n">
-        <v>232.2815068247954</v>
+        <v>202.092764919206</v>
       </c>
       <c r="D5" t="n">
-        <v>119.7732199181109</v>
+        <v>108.9249077861836</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.09694064747573</v>
+        <v>8.93586760405447</v>
       </c>
       <c r="C6" t="n">
-        <v>210.1538953187765</v>
+        <v>274.8383063084862</v>
       </c>
       <c r="D6" t="n">
-        <v>54.13847715069036</v>
+        <v>63.31585468998956</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>143.0691111921834</v>
+        <v>130.1336034410274</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>74.2692138262712</v>
+        <v>55.66018609227291</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.223478623669778</v>
+        <v>0.3632466505713198</v>
       </c>
       <c r="C2" t="n">
-        <v>3.309471511015998</v>
+        <v>1.579632056133118</v>
       </c>
       <c r="D2" t="n">
-        <v>12.07353326682727</v>
+        <v>6.94390151213769</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.04237938219863</v>
+        <v>2.827433388230814</v>
       </c>
       <c r="C3" t="n">
-        <v>19.48769192929919</v>
+        <v>13.8966387536136</v>
       </c>
       <c r="D3" t="n">
-        <v>67.72586537746621</v>
+        <v>52.17498174219674</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.52234050305086</v>
+        <v>8.857327787714723</v>
       </c>
       <c r="C4" t="n">
-        <v>95.2609432384765</v>
+        <v>48.26860762699868</v>
       </c>
       <c r="D4" t="n">
-        <v>154.0332695532118</v>
+        <v>120.5311291457894</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.31076602501908</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="C5" t="n">
-        <v>227.7163800000477</v>
+        <v>141.0035140224482</v>
       </c>
       <c r="D5" t="n">
-        <v>141.0771451002667</v>
+        <v>114.1527143112979</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.1258943569844</v>
+        <v>8.654106012935635</v>
       </c>
       <c r="C6" t="n">
-        <v>280.7955513778558</v>
+        <v>247.1854187229662</v>
       </c>
       <c r="D6" t="n">
-        <v>72.53348388516285</v>
+        <v>67.90454345963914</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.81679839440012</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C7" t="n">
-        <v>212.2980323048515</v>
+        <v>181.5762013958561</v>
       </c>
       <c r="D7" t="n">
-        <v>40.54323494228053</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.926230053461247</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>119.7486762255047</v>
+        <v>66.92574099850506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>29.84218496599028</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>18.93300447639974</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.986476516318797</v>
+        <v>0.1875138115111408</v>
       </c>
       <c r="C2" t="n">
-        <v>2.229549036344507</v>
+        <v>6.860452957276711</v>
       </c>
       <c r="D2" t="n">
-        <v>8.970228773703107</v>
+        <v>11.05546089752333</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86780821729195</v>
+        <v>1.963495408493621</v>
       </c>
       <c r="C3" t="n">
-        <v>16.86151682043897</v>
+        <v>9.257880851047423</v>
       </c>
       <c r="D3" t="n">
-        <v>63.80869203752144</v>
+        <v>45.62181581634928</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.09818443708723</v>
+        <v>7.070546965985528</v>
       </c>
       <c r="C4" t="n">
-        <v>78.46520351422208</v>
+        <v>40.3812465710798</v>
       </c>
       <c r="D4" t="n">
-        <v>153.5738116276243</v>
+        <v>119.7653659364769</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.74750488468867</v>
+        <v>13.67083678163684</v>
       </c>
       <c r="C5" t="n">
-        <v>214.1437179888356</v>
+        <v>113.0482481440202</v>
       </c>
       <c r="D5" t="n">
-        <v>155.8769917417874</v>
+        <v>132.1186972990145</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.3032718962836</v>
+        <v>13.44405306195583</v>
       </c>
       <c r="C6" t="n">
-        <v>320.2421741344926</v>
+        <v>236.1162133575834</v>
       </c>
       <c r="D6" t="n">
-        <v>85.29325879725866</v>
+        <v>87.54735152620934</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>275.0591995419416</v>
+        <v>278.1134166498534</v>
       </c>
       <c r="D7" t="n">
-        <v>45.27427712904591</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>158.3853571261379</v>
+        <v>156.8832831386403</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>58.46405753560178</v>
+        <v>56.68905768632355</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.038329218194631</v>
+        <v>0.186532063806894</v>
       </c>
       <c r="C2" t="n">
-        <v>6.90070461315083</v>
+        <v>13.19174390196439</v>
       </c>
       <c r="D2" t="n">
-        <v>18.10833640483242</v>
+        <v>12.43383467428585</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.19116306488765</v>
+        <v>1.256637061435917</v>
       </c>
       <c r="C3" t="n">
-        <v>13.05724446648258</v>
+        <v>19.17844140246144</v>
       </c>
       <c r="D3" t="n">
-        <v>58.06055922915637</v>
+        <v>44.31118263117979</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.8744848292392</v>
+        <v>5.385867905498002</v>
       </c>
       <c r="C4" t="n">
-        <v>62.53732876052182</v>
+        <v>30.69434197327653</v>
       </c>
       <c r="D4" t="n">
-        <v>149.0813341329909</v>
+        <v>114.7751423557904</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.58199043329844</v>
+        <v>12.2963899956913</v>
       </c>
       <c r="C5" t="n">
-        <v>184.7894616318559</v>
+        <v>92.67698328089891</v>
       </c>
       <c r="D5" t="n">
-        <v>169.8668965273044</v>
+        <v>145.0532233024663</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.38506005537235</v>
+        <v>16.14091400552181</v>
       </c>
       <c r="C6" t="n">
-        <v>329.1780417385471</v>
+        <v>208.7450873631823</v>
       </c>
       <c r="D6" t="n">
-        <v>105.4593383901924</v>
+        <v>107.3914178721501</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.06981156465531</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>347.941203862112</v>
+        <v>313.0871968659418</v>
       </c>
       <c r="D7" t="n">
-        <v>54.37704184282233</v>
+        <v>58.09001166028376</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>236.99389580518</v>
+        <v>263.0298449218054</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>106.6109284472738</v>
+        <v>123.5843645059969</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>25.73749781453438</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>46.40721397974673</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.088038498212724</v>
+        <v>2.826451640526567</v>
       </c>
       <c r="C2" t="n">
-        <v>3.390956570468483</v>
+        <v>3.721805546799658</v>
       </c>
       <c r="D2" t="n">
-        <v>8.288895866955821</v>
+        <v>7.442629345895069</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.645229225868407</v>
+        <v>0.3612831551628262</v>
       </c>
       <c r="C2" t="n">
-        <v>4.02909257822891</v>
+        <v>23.55114567717673</v>
       </c>
       <c r="D2" t="n">
-        <v>13.47252374537898</v>
+        <v>11.60916660271853</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.45333075965055</v>
+        <v>0.937569057555704</v>
       </c>
       <c r="C3" t="n">
-        <v>18.85937339858123</v>
+        <v>35.58835427894688</v>
       </c>
       <c r="D3" t="n">
-        <v>64.65790380169493</v>
+        <v>43.76140391680158</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.39846036586651</v>
+        <v>3.892629647338604</v>
       </c>
       <c r="C4" t="n">
-        <v>94.32926466714628</v>
+        <v>39.24536447726624</v>
       </c>
       <c r="D4" t="n">
-        <v>154.288523956316</v>
+        <v>111.3547333541945</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.245986372072</v>
+        <v>10.55378782065321</v>
       </c>
       <c r="C5" t="n">
-        <v>276.4110661306895</v>
+        <v>75.22641783791185</v>
       </c>
       <c r="D5" t="n">
-        <v>154.4289138780233</v>
+        <v>150.8700784501286</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98369550412208</v>
+        <v>16.46292725251477</v>
       </c>
       <c r="C6" t="n">
-        <v>290.4559487876444</v>
+        <v>179.60288851032</v>
       </c>
       <c r="D6" t="n">
-        <v>81.79136473621028</v>
+        <v>125.9876828859932</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>166.6644355160512</v>
+        <v>311.8295780568016</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>71.86393195086652</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>78.52509012418112</v>
+        <v>335.88043331544</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>213.1109194039678</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>90.25206645140929</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.937430188835462</v>
+        <v>3.765002445786517</v>
       </c>
       <c r="C2" t="n">
-        <v>5.709844647899449</v>
+        <v>8.013024762062466</v>
       </c>
       <c r="D2" t="n">
-        <v>13.32918858055894</v>
+        <v>12.19821522526662</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.29134238844982</v>
+        <v>4.678027810736052</v>
       </c>
       <c r="C3" t="n">
-        <v>8.541205026947251</v>
+        <v>7.348381566287376</v>
       </c>
       <c r="D3" t="n">
-        <v>10.09727513817845</v>
+        <v>8.128870991163589</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.44074796594459</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39843681825034</v>
+        <v>11.67906960599909</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14475746025178</v>
+        <v>59.95255731079536</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57628668450004</v>
+        <v>0.7786046403999396</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.126105674500097</v>
+        <v>2.111739311834889</v>
       </c>
       <c r="C2" t="n">
-        <v>8.103345550853172</v>
+        <v>9.021279654323941</v>
       </c>
       <c r="D2" t="n">
-        <v>28.69255840431728</v>
+        <v>21.2391298336755</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.24425955637498</v>
+        <v>10.11200135374215</v>
       </c>
       <c r="C3" t="n">
-        <v>17.12658870058561</v>
+        <v>23.30178176029805</v>
       </c>
       <c r="D3" t="n">
-        <v>18.84955592153876</v>
+        <v>16.81733817374786</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.21989579021806</v>
+        <v>5.960190312482386</v>
       </c>
       <c r="C4" t="n">
-        <v>13.55400880483146</v>
+        <v>12.52022847225957</v>
       </c>
       <c r="D4" t="n">
-        <v>20.35653864755761</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44235287899692</v>
+        <v>13.6337107211819</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15207395650914</v>
+        <v>73.78243449110207</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251021658736194</v>
+        <v>1.603965967197871</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.238605749860979</v>
+        <v>1.253691818323177</v>
       </c>
       <c r="C2" t="n">
-        <v>4.122358610132356</v>
+        <v>9.957866964175397</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99395494952105</v>
+        <v>21.61415745669778</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.54092728950677</v>
+        <v>8.609927366244527</v>
       </c>
       <c r="C3" t="n">
-        <v>25.86414326838222</v>
+        <v>31.00850123863551</v>
       </c>
       <c r="D3" t="n">
-        <v>37.42913122440964</v>
+        <v>30.59125846433061</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.34822700203391</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C4" t="n">
-        <v>30.8092064546734</v>
+        <v>41.32568786256524</v>
       </c>
       <c r="D4" t="n">
-        <v>25.23189774684727</v>
+        <v>22.80698091735765</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.62866268808323</v>
+        <v>6.111379458936396</v>
       </c>
       <c r="C5" t="n">
-        <v>16.5915362017711</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="D5" t="n">
-        <v>29.77149913128453</v>
+        <v>26.72808124811942</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.735117543052</v>
+        <v>14.84973541294661</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0842170126172</v>
+        <v>87.44844187624112</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020535262915601</v>
+        <v>2.474955902157768</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.992587986722531</v>
+        <v>1.607120991852028</v>
       </c>
       <c r="C2" t="n">
-        <v>6.245878894418207</v>
+        <v>11.07509585160827</v>
       </c>
       <c r="D2" t="n">
-        <v>35.27615850899639</v>
+        <v>22.12073927208913</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0227444281137</v>
+        <v>6.175193059712438</v>
       </c>
       <c r="C3" t="n">
-        <v>20.15528036818702</v>
+        <v>35.80433877388118</v>
       </c>
       <c r="D3" t="n">
-        <v>51.13923791421635</v>
+        <v>40.7817996344125</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.49611105247669</v>
+        <v>15.67262035059608</v>
       </c>
       <c r="C4" t="n">
-        <v>49.74908316500287</v>
+        <v>63.09888844735099</v>
       </c>
       <c r="D4" t="n">
-        <v>37.61173629739955</v>
+        <v>32.77466535857552</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.42283982755667</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C5" t="n">
-        <v>38.18998569520093</v>
+        <v>51.02633692822798</v>
       </c>
       <c r="D5" t="n">
-        <v>31.80862561759666</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.57739082328414</v>
+        <v>6.601271563355554</v>
       </c>
       <c r="C6" t="n">
-        <v>19.64280806657019</v>
+        <v>18.8377749490878</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05998295511477</v>
+        <v>16.09993810235912</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8198888024154</v>
+        <v>101.6838195938471</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879993506710388</v>
+        <v>3.389460653128236</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.856525966459724</v>
+        <v>1.522690689286803</v>
       </c>
       <c r="C2" t="n">
-        <v>12.07549676223577</v>
+        <v>7.085273181549231</v>
       </c>
       <c r="D2" t="n">
-        <v>31.77917318646925</v>
+        <v>22.18749811597791</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.06906649666254</v>
+        <v>5.816855147662352</v>
       </c>
       <c r="C3" t="n">
-        <v>21.1468455494763</v>
+        <v>40.0307626406637</v>
       </c>
       <c r="D3" t="n">
-        <v>62.63059479242527</v>
+        <v>48.5228802823986</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.57573042751191</v>
+        <v>13.77097504747001</v>
       </c>
       <c r="C4" t="n">
-        <v>41.93829843001524</v>
+        <v>78.1971863909627</v>
       </c>
       <c r="D4" t="n">
-        <v>47.01786105178824</v>
+        <v>44.82267318509238</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.06602344255857</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C5" t="n">
-        <v>49.50462798664542</v>
+        <v>87.0810213666921</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>34.45934441906305</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.63022527286423</v>
+        <v>13.00128484734051</v>
       </c>
       <c r="C6" t="n">
-        <v>27.81389420901639</v>
+        <v>51.40136455125026</v>
       </c>
       <c r="D6" t="n">
-        <v>30.87302005544945</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>16.04961146902685</v>
+        <v>22.75691178444107</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057732677492689</v>
+        <v>17.37684076477732</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16624385149396</v>
+        <v>115.5559910857692</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293299508119516</v>
+        <v>4.344210191194329</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.486006171331176</v>
+        <v>1.862375394956199</v>
       </c>
       <c r="C2" t="n">
-        <v>7.281622722398593</v>
+        <v>5.334817024877167</v>
       </c>
       <c r="D2" t="n">
-        <v>25.75222403009808</v>
+        <v>35.86717062695297</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.77025534167302</v>
+        <v>5.4634259741335</v>
       </c>
       <c r="C3" t="n">
-        <v>37.93964003061799</v>
+        <v>32.97690538565036</v>
       </c>
       <c r="D3" t="n">
-        <v>74.19067400993146</v>
+        <v>54.16792958181776</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.13202152292136</v>
+        <v>12.48194031179395</v>
       </c>
       <c r="C4" t="n">
-        <v>48.94503179522473</v>
+        <v>89.97717709422018</v>
       </c>
       <c r="D4" t="n">
-        <v>68.484756352849</v>
+        <v>57.07488453409257</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.04272353956391</v>
+        <v>19.9785657814226</v>
       </c>
       <c r="C5" t="n">
-        <v>66.70975650357077</v>
+        <v>116.8525204979766</v>
       </c>
       <c r="D5" t="n">
-        <v>41.55247158224626</v>
+        <v>42.3378697456437</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>19.40129813132547</v>
       </c>
       <c r="C6" t="n">
-        <v>57.39886127649402</v>
+        <v>94.71214627180255</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.97165248976386</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>30.42239785920016</v>
+        <v>47.78951474732623</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>20.5283444958008</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279310331732048</v>
+        <v>18.67382223611215</v>
       </c>
       <c r="C21" t="n">
-        <v>75.52284469172001</v>
+        <v>128.9382963922029</v>
       </c>
       <c r="D21" t="n">
-        <v>6.369396540265542</v>
+        <v>5.335377781746328</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.997496725243765</v>
+        <v>1.657190124768616</v>
       </c>
       <c r="C2" t="n">
-        <v>7.437720607373835</v>
+        <v>3.285909566114074</v>
       </c>
       <c r="D2" t="n">
-        <v>26.161612822769</v>
+        <v>28.0406779286974</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.20927649192059</v>
+        <v>7.903069019186823</v>
       </c>
       <c r="C3" t="n">
-        <v>32.11296740591317</v>
+        <v>47.86020058203201</v>
       </c>
       <c r="D3" t="n">
-        <v>77.57770358958295</v>
+        <v>61.37395773098935</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.5817030291954</v>
+        <v>9.59756555671682</v>
       </c>
       <c r="C4" t="n">
-        <v>76.06581212504287</v>
+        <v>115.3367020426195</v>
       </c>
       <c r="D4" t="n">
-        <v>90.28348237794518</v>
+        <v>53.47579745032376</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.47317100238052</v>
+        <v>10.92194320974577</v>
       </c>
       <c r="C5" t="n">
-        <v>80.30696220738911</v>
+        <v>56.57321145722246</v>
       </c>
       <c r="D5" t="n">
-        <v>56.32777453116076</v>
+        <v>35.68652904937156</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.42524529132167</v>
+        <v>6.963536466222627</v>
       </c>
       <c r="C6" t="n">
-        <v>84.16621243278331</v>
+        <v>31.47679489356124</v>
       </c>
       <c r="D6" t="n">
-        <v>39.7686360036298</v>
+        <v>25.27803988894688</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.4698816019025</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>58.62899114991527</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>27.60772719112455</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>25.18281036163492</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.488090265025561</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.24101548153756</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.488090265025561</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
